--- a/artfynd/A 49797-2025 artfynd.xlsx
+++ b/artfynd/A 49797-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2009,37 +2009,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129797295</v>
+        <v>129797289</v>
       </c>
       <c r="B12" t="n">
-        <v>80090</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2047,10 +2052,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>424583</v>
+        <v>424665</v>
       </c>
       <c r="R12" t="n">
-        <v>6957891</v>
+        <v>6957984</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2087,7 +2092,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På en gammal asp.</t>
+          <t>Ringhack, äldre, nästan på gränsen till färska, på stambasen av en gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2096,7 +2101,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2107,22 +2111,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2140,42 +2144,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129797289</v>
+        <v>129797295</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>80090</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2183,10 +2182,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>424665</v>
+        <v>424583</v>
       </c>
       <c r="R13" t="n">
-        <v>6957984</v>
+        <v>6957891</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2223,7 +2222,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, nästan på gränsen till färska, på stambasen av en gran i barrblandskog.</t>
+          <t>På en gammal asp.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2232,6 +2231,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2242,22 +2242,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2666,6 +2666,3258 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129805503</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>424507</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6958067</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre på tall</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129805493</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>424319</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6958042</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129805487</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>424741</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6957878</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129805517</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>424426</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6958107</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129805508</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>424626</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6957996</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre på tall</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129805504</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>424513</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6958070</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129805511</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>424758</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6957908</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129805506</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>424593</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6958056</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129805488</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>424434</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6957942</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129805486</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>424588</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6957887</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Gammalt bohål 2m upp i klen asp</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129805513</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>424735</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6957898</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129805514</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>424899</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6957678</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129805497</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>424480</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6958080</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129805520</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91613</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>424860</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6957844</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129805492</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>424403</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6958029</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129805496</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>424489</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6958088</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129805494</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>424372</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6958049</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129805498</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>424462</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6958065</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129805505</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>424516</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6958064</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre på tall</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129805495</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>424572</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6958078</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129805509</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>424763</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6957936</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129805507</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>424614</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6957999</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre på tall</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129805510</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>424762</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6957913</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129805501</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>424430</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6958097</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129805490</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>424603</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6957917</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre på tall</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129805519</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91613</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>424761</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6957912</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129805500</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>424455</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6958082</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129805515</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>424548</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6957946</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129805491</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>424474</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6957973</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129805502</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>424416</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6958115</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129805516</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91614</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>424426</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6958107</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129805512</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lövsta, Hjd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>424748</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6957908</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49797-2025 artfynd.xlsx
+++ b/artfynd/A 49797-2025 artfynd.xlsx
@@ -3896,10 +3896,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129805497</v>
+        <v>129805520</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>91613</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,23 +3907,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3931,10 +3927,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>424480</v>
+        <v>424860</v>
       </c>
       <c r="R29" t="n">
-        <v>6958080</v>
+        <v>6957844</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3967,11 +3963,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3998,10 +3989,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129805520</v>
+        <v>129805497</v>
       </c>
       <c r="B30" t="n">
-        <v>91613</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4009,19 +4000,23 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4029,10 +4024,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>424860</v>
+        <v>424480</v>
       </c>
       <c r="R30" t="n">
-        <v>6957844</v>
+        <v>6958080</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4065,6 +4060,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 49797-2025 artfynd.xlsx
+++ b/artfynd/A 49797-2025 artfynd.xlsx
@@ -1338,7 +1338,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129797288</v>
+        <v>129797293</v>
       </c>
       <c r="B7" t="n">
         <v>57736</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>424643</v>
+        <v>424901</v>
       </c>
       <c r="R7" t="n">
-        <v>6958012</v>
+        <v>6957647</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
+          <t>Ringhack, äldre, på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129797293</v>
+        <v>129797288</v>
       </c>
       <c r="B8" t="n">
         <v>57736</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>424901</v>
+        <v>424643</v>
       </c>
       <c r="R8" t="n">
-        <v>6957647</v>
+        <v>6958012</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall.</t>
+          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1570,17 +1570,17 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -2009,42 +2009,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129797289</v>
+        <v>129797295</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>80090</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2052,10 +2047,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>424665</v>
+        <v>424583</v>
       </c>
       <c r="R12" t="n">
-        <v>6957984</v>
+        <v>6957891</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2092,7 +2087,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, nästan på gränsen till färska, på stambasen av en gran i barrblandskog.</t>
+          <t>På en gammal asp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2101,6 +2096,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2111,22 +2107,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2144,37 +2140,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129797295</v>
+        <v>129797289</v>
       </c>
       <c r="B13" t="n">
-        <v>80090</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2182,10 +2183,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>424583</v>
+        <v>424665</v>
       </c>
       <c r="R13" t="n">
-        <v>6957891</v>
+        <v>6957984</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2222,7 +2223,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På en gammal asp.</t>
+          <t>Ringhack, äldre, nästan på gränsen till färska, på stambasen av en gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2231,7 +2232,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2242,22 +2242,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -3896,10 +3896,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129805520</v>
+        <v>129805497</v>
       </c>
       <c r="B29" t="n">
-        <v>91613</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,19 +3907,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3927,10 +3931,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>424860</v>
+        <v>424480</v>
       </c>
       <c r="R29" t="n">
-        <v>6957844</v>
+        <v>6958080</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3963,6 +3967,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3989,10 +3998,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129805497</v>
+        <v>129805520</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>91613</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4000,23 +4009,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4024,10 +4029,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>424480</v>
+        <v>424860</v>
       </c>
       <c r="R30" t="n">
-        <v>6958080</v>
+        <v>6957844</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4060,11 +4065,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -5408,10 +5408,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129805515</v>
+        <v>129805491</v>
       </c>
       <c r="B44" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5419,46 +5419,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>424548</v>
+        <v>424474</v>
       </c>
       <c r="R44" t="n">
-        <v>6957946</v>
+        <v>6957973</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5491,6 +5479,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5517,10 +5510,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129805491</v>
+        <v>129805515</v>
       </c>
       <c r="B45" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5528,34 +5521,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>424474</v>
+        <v>424548</v>
       </c>
       <c r="R45" t="n">
-        <v>6957973</v>
+        <v>6957946</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5588,11 +5593,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 49797-2025 artfynd.xlsx
+++ b/artfynd/A 49797-2025 artfynd.xlsx
@@ -1338,7 +1338,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129797293</v>
+        <v>129797288</v>
       </c>
       <c r="B7" t="n">
         <v>57736</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>424901</v>
+        <v>424643</v>
       </c>
       <c r="R7" t="n">
-        <v>6957647</v>
+        <v>6958012</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall.</t>
+          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129797288</v>
+        <v>129797293</v>
       </c>
       <c r="B8" t="n">
         <v>57736</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>424643</v>
+        <v>424901</v>
       </c>
       <c r="R8" t="n">
-        <v>6958012</v>
+        <v>6957647</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
+          <t>Ringhack, äldre, på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1570,17 +1570,17 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1746,7 +1746,7 @@
         <v>129797299</v>
       </c>
       <c r="B10" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3896,10 +3896,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129805497</v>
+        <v>129805520</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>91617</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,23 +3907,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3931,10 +3927,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>424480</v>
+        <v>424860</v>
       </c>
       <c r="R29" t="n">
-        <v>6958080</v>
+        <v>6957844</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3967,11 +3963,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3998,10 +3989,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129805520</v>
+        <v>129805497</v>
       </c>
       <c r="B30" t="n">
-        <v>91613</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4009,19 +4000,23 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4029,10 +4024,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>424860</v>
+        <v>424480</v>
       </c>
       <c r="R30" t="n">
-        <v>6957844</v>
+        <v>6958080</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4065,6 +4060,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -5216,7 +5216,7 @@
         <v>129805519</v>
       </c>
       <c r="B42" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5408,10 +5408,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129805491</v>
+        <v>129805515</v>
       </c>
       <c r="B44" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5419,34 +5419,46 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>424474</v>
+        <v>424548</v>
       </c>
       <c r="R44" t="n">
-        <v>6957973</v>
+        <v>6957946</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5479,11 +5491,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5510,10 +5517,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129805515</v>
+        <v>129805491</v>
       </c>
       <c r="B45" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5521,46 +5528,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>424548</v>
+        <v>424474</v>
       </c>
       <c r="R45" t="n">
-        <v>6957946</v>
+        <v>6957973</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5593,6 +5588,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5724,7 +5724,7 @@
         <v>129805516</v>
       </c>
       <c r="B47" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 49797-2025 artfynd.xlsx
+++ b/artfynd/A 49797-2025 artfynd.xlsx
@@ -1746,7 +1746,7 @@
         <v>129797299</v>
       </c>
       <c r="B10" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>129805520</v>
       </c>
       <c r="B29" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>129805519</v>
       </c>
       <c r="B42" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5408,10 +5408,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129805515</v>
+        <v>129805491</v>
       </c>
       <c r="B44" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5419,46 +5419,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>424548</v>
+        <v>424474</v>
       </c>
       <c r="R44" t="n">
-        <v>6957946</v>
+        <v>6957973</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5491,6 +5479,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5517,10 +5510,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129805491</v>
+        <v>129805515</v>
       </c>
       <c r="B45" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5528,34 +5521,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>424474</v>
+        <v>424548</v>
       </c>
       <c r="R45" t="n">
-        <v>6957973</v>
+        <v>6957946</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5588,11 +5593,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5724,7 +5724,7 @@
         <v>129805516</v>
       </c>
       <c r="B47" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 49797-2025 artfynd.xlsx
+++ b/artfynd/A 49797-2025 artfynd.xlsx
@@ -3896,10 +3896,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129805520</v>
+        <v>129805497</v>
       </c>
       <c r="B29" t="n">
-        <v>91619</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,19 +3907,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3927,10 +3931,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>424860</v>
+        <v>424480</v>
       </c>
       <c r="R29" t="n">
-        <v>6957844</v>
+        <v>6958080</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3963,6 +3967,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3989,10 +3998,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129805497</v>
+        <v>129805520</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>91619</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4000,23 +4009,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4024,10 +4029,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>424480</v>
+        <v>424860</v>
       </c>
       <c r="R30" t="n">
-        <v>6958080</v>
+        <v>6957844</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4060,11 +4065,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 49797-2025 artfynd.xlsx
+++ b/artfynd/A 49797-2025 artfynd.xlsx
@@ -3896,10 +3896,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129805497</v>
+        <v>129805520</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>91619</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,23 +3907,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3931,10 +3927,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>424480</v>
+        <v>424860</v>
       </c>
       <c r="R29" t="n">
-        <v>6958080</v>
+        <v>6957844</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3967,11 +3963,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3998,10 +3989,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129805520</v>
+        <v>129805497</v>
       </c>
       <c r="B30" t="n">
-        <v>91619</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4009,19 +4000,23 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4029,10 +4024,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>424860</v>
+        <v>424480</v>
       </c>
       <c r="R30" t="n">
-        <v>6957844</v>
+        <v>6958080</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4065,6 +4060,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 49797-2025 artfynd.xlsx
+++ b/artfynd/A 49797-2025 artfynd.xlsx
@@ -3590,7 +3590,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129805486</v>
+        <v>129805513</v>
       </c>
       <c r="B26" t="n">
         <v>57736</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>424588</v>
+        <v>424735</v>
       </c>
       <c r="R26" t="n">
-        <v>6957887</v>
+        <v>6957898</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gammalt bohål 2m upp i klen asp</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3692,7 +3692,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129805513</v>
+        <v>129805514</v>
       </c>
       <c r="B27" t="n">
         <v>57736</v>
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>424735</v>
+        <v>424899</v>
       </c>
       <c r="R27" t="n">
-        <v>6957898</v>
+        <v>6957678</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3794,7 +3794,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129805514</v>
+        <v>129805486</v>
       </c>
       <c r="B28" t="n">
         <v>57736</v>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>424899</v>
+        <v>424588</v>
       </c>
       <c r="R28" t="n">
-        <v>6957678</v>
+        <v>6957887</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Gammalt bohål 2m upp i klen asp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3896,10 +3896,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129805520</v>
+        <v>129805497</v>
       </c>
       <c r="B29" t="n">
-        <v>91619</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,19 +3907,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3927,10 +3931,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>424860</v>
+        <v>424480</v>
       </c>
       <c r="R29" t="n">
-        <v>6957844</v>
+        <v>6958080</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3963,6 +3967,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3989,10 +3998,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129805497</v>
+        <v>129805520</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>91619</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4000,23 +4009,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4024,10 +4029,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>424480</v>
+        <v>424860</v>
       </c>
       <c r="R30" t="n">
-        <v>6958080</v>
+        <v>6957844</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4060,11 +4065,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 49797-2025 artfynd.xlsx
+++ b/artfynd/A 49797-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129797291</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>129797285</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>129797297</v>
       </c>
       <c r="B4" t="n">
-        <v>57840</v>
+        <v>57841</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129797283</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>129797284</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>129797288</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>129797293</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>129797296</v>
       </c>
       <c r="B9" t="n">
-        <v>80222</v>
+        <v>80225</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>129797299</v>
       </c>
       <c r="B10" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>129797287</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>129797295</v>
       </c>
       <c r="B12" t="n">
-        <v>80090</v>
+        <v>80093</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>129797289</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>129797294</v>
       </c>
       <c r="B14" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>129797292</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>129797290</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>129805503</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>129805493</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>129805487</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>129805517</v>
       </c>
       <c r="B20" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3080,10 +3080,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129805508</v>
+        <v>129805504</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>424626</v>
+        <v>424513</v>
       </c>
       <c r="R21" t="n">
-        <v>6957996</v>
+        <v>6958070</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre på tall</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3182,10 +3182,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129805504</v>
+        <v>129805508</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>424513</v>
+        <v>424626</v>
       </c>
       <c r="R22" t="n">
-        <v>6958070</v>
+        <v>6957996</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3287,7 +3287,7 @@
         <v>129805511</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>129805506</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>129805488</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3590,10 +3590,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129805513</v>
+        <v>129805486</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>424735</v>
+        <v>424588</v>
       </c>
       <c r="R26" t="n">
-        <v>6957898</v>
+        <v>6957887</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gammalt bohål 2m upp i klen asp</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3692,10 +3692,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129805514</v>
+        <v>129805513</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>424899</v>
+        <v>424735</v>
       </c>
       <c r="R27" t="n">
-        <v>6957678</v>
+        <v>6957898</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3794,10 +3794,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129805486</v>
+        <v>129805514</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>424588</v>
+        <v>424899</v>
       </c>
       <c r="R28" t="n">
-        <v>6957887</v>
+        <v>6957678</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Gammalt bohål 2m upp i klen asp</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3896,10 +3896,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129805497</v>
+        <v>129805520</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>91622</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,23 +3907,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3931,10 +3927,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>424480</v>
+        <v>424860</v>
       </c>
       <c r="R29" t="n">
-        <v>6958080</v>
+        <v>6957844</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3967,11 +3963,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3998,10 +3989,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129805520</v>
+        <v>129805497</v>
       </c>
       <c r="B30" t="n">
-        <v>91619</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4009,19 +4000,23 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4029,10 +4024,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>424860</v>
+        <v>424480</v>
       </c>
       <c r="R30" t="n">
-        <v>6957844</v>
+        <v>6958080</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4065,6 +4060,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4094,7 +4094,7 @@
         <v>129805492</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>129805496</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>129805494</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>129805498</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>129805505</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>129805495</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>129805509</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>129805507</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>129805510</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>129805501</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>129805490</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>129805519</v>
       </c>
       <c r="B42" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>129805500</v>
       </c>
       <c r="B43" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>129805491</v>
       </c>
       <c r="B44" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>129805515</v>
       </c>
       <c r="B45" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>129805502</v>
       </c>
       <c r="B46" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>129805516</v>
       </c>
       <c r="B47" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>129805512</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 49797-2025 artfynd.xlsx
+++ b/artfynd/A 49797-2025 artfynd.xlsx
@@ -1203,7 +1203,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129797284</v>
+        <v>129797293</v>
       </c>
       <c r="B6" t="n">
         <v>57737</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>424412</v>
+        <v>424901</v>
       </c>
       <c r="R6" t="n">
-        <v>6957972</v>
+        <v>6957647</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran med full längd och 33 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, äldre, på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,27 +1300,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1338,7 +1338,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129797288</v>
+        <v>129797284</v>
       </c>
       <c r="B7" t="n">
         <v>57737</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>424643</v>
+        <v>424412</v>
       </c>
       <c r="R7" t="n">
-        <v>6958012</v>
+        <v>6957972</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
+          <t>Ringhack, äldre, på en stående död gran med full längd och 33 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129797293</v>
+        <v>129797288</v>
       </c>
       <c r="B8" t="n">
         <v>57737</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>424901</v>
+        <v>424643</v>
       </c>
       <c r="R8" t="n">
-        <v>6957647</v>
+        <v>6958012</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall.</t>
+          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1570,17 +1570,17 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1743,10 +1743,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129797299</v>
+        <v>129797287</v>
       </c>
       <c r="B10" t="n">
-        <v>91622</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,24 +1754,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1781,10 +1786,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>424431</v>
+        <v>424588</v>
       </c>
       <c r="R10" t="n">
-        <v>6957958</v>
+        <v>6958061</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1821,7 +1826,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en granhögstubbe med bohål.</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en flerstammig gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1830,7 +1835,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1851,12 +1855,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1874,10 +1878,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129797287</v>
+        <v>129797299</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>91622</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1885,29 +1889,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1917,10 +1916,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>424588</v>
+        <v>424431</v>
       </c>
       <c r="R11" t="n">
-        <v>6958061</v>
+        <v>6957958</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1957,7 +1956,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en flerstammig gran.</t>
+          <t>Flera fruktkroppar i en granhögstubbe med bohål.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1966,6 +1965,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1986,12 +1986,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2009,37 +2009,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129797295</v>
+        <v>129797289</v>
       </c>
       <c r="B12" t="n">
-        <v>80093</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2047,10 +2052,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>424583</v>
+        <v>424665</v>
       </c>
       <c r="R12" t="n">
-        <v>6957891</v>
+        <v>6957984</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2087,7 +2092,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På en gammal asp.</t>
+          <t>Ringhack, äldre, nästan på gränsen till färska, på stambasen av en gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2096,7 +2101,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2107,22 +2111,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2140,42 +2144,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129797289</v>
+        <v>129797295</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>80093</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2183,10 +2182,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>424665</v>
+        <v>424583</v>
       </c>
       <c r="R13" t="n">
-        <v>6957984</v>
+        <v>6957891</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2223,7 +2222,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, nästan på gränsen till färska, på stambasen av en gran i barrblandskog.</t>
+          <t>På en gammal asp.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2232,6 +2231,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2242,22 +2242,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -3080,7 +3080,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129805504</v>
+        <v>129805508</v>
       </c>
       <c r="B21" t="n">
         <v>57737</v>
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>424513</v>
+        <v>424626</v>
       </c>
       <c r="R21" t="n">
-        <v>6958070</v>
+        <v>6957996</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3182,7 +3182,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129805508</v>
+        <v>129805504</v>
       </c>
       <c r="B22" t="n">
         <v>57737</v>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>424626</v>
+        <v>424513</v>
       </c>
       <c r="R22" t="n">
-        <v>6957996</v>
+        <v>6958070</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre på tall</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -5408,10 +5408,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129805491</v>
+        <v>129805515</v>
       </c>
       <c r="B44" t="n">
-        <v>57737</v>
+        <v>57895</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5419,34 +5419,46 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>424474</v>
+        <v>424548</v>
       </c>
       <c r="R44" t="n">
-        <v>6957973</v>
+        <v>6957946</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5479,11 +5491,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5510,10 +5517,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129805515</v>
+        <v>129805491</v>
       </c>
       <c r="B45" t="n">
-        <v>57895</v>
+        <v>57737</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5521,46 +5528,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>424548</v>
+        <v>424474</v>
       </c>
       <c r="R45" t="n">
-        <v>6957946</v>
+        <v>6957973</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5593,6 +5588,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 49797-2025 artfynd.xlsx
+++ b/artfynd/A 49797-2025 artfynd.xlsx
@@ -1203,7 +1203,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129797293</v>
+        <v>129797284</v>
       </c>
       <c r="B6" t="n">
         <v>57737</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>424901</v>
+        <v>424412</v>
       </c>
       <c r="R6" t="n">
-        <v>6957647</v>
+        <v>6957972</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall.</t>
+          <t>Ringhack, äldre, på en stående död gran med full längd och 33 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,27 +1300,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1338,7 +1338,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129797284</v>
+        <v>129797288</v>
       </c>
       <c r="B7" t="n">
         <v>57737</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>424412</v>
+        <v>424643</v>
       </c>
       <c r="R7" t="n">
-        <v>6957972</v>
+        <v>6958012</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran med full längd och 33 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129797288</v>
+        <v>129797293</v>
       </c>
       <c r="B8" t="n">
         <v>57737</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>424643</v>
+        <v>424901</v>
       </c>
       <c r="R8" t="n">
-        <v>6958012</v>
+        <v>6957647</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
+          <t>Ringhack, äldre, på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1570,17 +1570,17 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129805515</v>
+        <v>129805491</v>
       </c>
       <c r="B44" t="n">
-        <v>57895</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5419,46 +5419,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>424548</v>
+        <v>424474</v>
       </c>
       <c r="R44" t="n">
-        <v>6957946</v>
+        <v>6957973</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5491,6 +5479,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5517,10 +5510,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129805491</v>
+        <v>129805515</v>
       </c>
       <c r="B45" t="n">
-        <v>57737</v>
+        <v>57895</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5528,34 +5521,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>424474</v>
+        <v>424548</v>
       </c>
       <c r="R45" t="n">
-        <v>6957973</v>
+        <v>6957946</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5588,11 +5593,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 49797-2025 artfynd.xlsx
+++ b/artfynd/A 49797-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129797291</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>129797285</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>129797297</v>
       </c>
       <c r="B4" t="n">
-        <v>57841</v>
+        <v>57844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129797283</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>129797284</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>129797288</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>129797293</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>129797296</v>
       </c>
       <c r="B9" t="n">
-        <v>80225</v>
+        <v>80228</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1743,10 +1743,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129797287</v>
+        <v>129797299</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>91625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,29 +1754,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1786,10 +1781,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>424588</v>
+        <v>424431</v>
       </c>
       <c r="R10" t="n">
-        <v>6958061</v>
+        <v>6957958</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1826,7 +1821,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en flerstammig gran.</t>
+          <t>Flera fruktkroppar i en granhögstubbe med bohål.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1835,6 +1830,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1855,12 +1851,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1878,10 +1874,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129797299</v>
+        <v>129797287</v>
       </c>
       <c r="B11" t="n">
-        <v>91622</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,24 +1885,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1916,10 +1917,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>424431</v>
+        <v>424588</v>
       </c>
       <c r="R11" t="n">
-        <v>6957958</v>
+        <v>6958061</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1956,7 +1957,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en granhögstubbe med bohål.</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en flerstammig gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1965,7 +1966,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1986,12 +1986,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2009,42 +2009,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129797289</v>
+        <v>129797295</v>
       </c>
       <c r="B12" t="n">
-        <v>57737</v>
+        <v>80096</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2052,10 +2047,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>424665</v>
+        <v>424583</v>
       </c>
       <c r="R12" t="n">
-        <v>6957984</v>
+        <v>6957891</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2092,7 +2087,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, nästan på gränsen till färska, på stambasen av en gran i barrblandskog.</t>
+          <t>På en gammal asp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2101,6 +2096,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2111,22 +2107,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2144,37 +2140,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129797295</v>
+        <v>129797289</v>
       </c>
       <c r="B13" t="n">
-        <v>80093</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2182,10 +2183,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>424583</v>
+        <v>424665</v>
       </c>
       <c r="R13" t="n">
-        <v>6957891</v>
+        <v>6957984</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2222,7 +2223,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På en gammal asp.</t>
+          <t>Ringhack, äldre, nästan på gränsen till färska, på stambasen av en gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2231,7 +2232,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2242,22 +2242,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2278,7 +2278,7 @@
         <v>129797294</v>
       </c>
       <c r="B14" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>129797292</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>129797290</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>129805503</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>129805493</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>129805487</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>129805517</v>
       </c>
       <c r="B20" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>129805508</v>
       </c>
       <c r="B21" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>129805504</v>
       </c>
       <c r="B22" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>129805511</v>
       </c>
       <c r="B23" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>129805506</v>
       </c>
       <c r="B24" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>129805488</v>
       </c>
       <c r="B25" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>129805486</v>
       </c>
       <c r="B26" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>129805513</v>
       </c>
       <c r="B27" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>129805514</v>
       </c>
       <c r="B28" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3896,10 +3896,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129805520</v>
+        <v>129805497</v>
       </c>
       <c r="B29" t="n">
-        <v>91622</v>
+        <v>57740</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,19 +3907,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3927,10 +3931,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>424860</v>
+        <v>424480</v>
       </c>
       <c r="R29" t="n">
-        <v>6957844</v>
+        <v>6958080</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3963,6 +3967,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3989,10 +3998,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129805497</v>
+        <v>129805520</v>
       </c>
       <c r="B30" t="n">
-        <v>57737</v>
+        <v>91625</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4000,23 +4009,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4024,10 +4029,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>424480</v>
+        <v>424860</v>
       </c>
       <c r="R30" t="n">
-        <v>6958080</v>
+        <v>6957844</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4060,11 +4065,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4094,7 +4094,7 @@
         <v>129805492</v>
       </c>
       <c r="B31" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>129805496</v>
       </c>
       <c r="B32" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>129805494</v>
       </c>
       <c r="B33" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>129805498</v>
       </c>
       <c r="B34" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>129805505</v>
       </c>
       <c r="B35" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>129805495</v>
       </c>
       <c r="B36" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>129805509</v>
       </c>
       <c r="B37" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>129805507</v>
       </c>
       <c r="B38" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>129805510</v>
       </c>
       <c r="B39" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>129805501</v>
       </c>
       <c r="B40" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>129805490</v>
       </c>
       <c r="B41" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>129805519</v>
       </c>
       <c r="B42" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>129805500</v>
       </c>
       <c r="B43" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5408,10 +5408,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129805491</v>
+        <v>129805515</v>
       </c>
       <c r="B44" t="n">
-        <v>57737</v>
+        <v>57898</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5419,34 +5419,46 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>424474</v>
+        <v>424548</v>
       </c>
       <c r="R44" t="n">
-        <v>6957973</v>
+        <v>6957946</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5479,11 +5491,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5510,10 +5517,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129805515</v>
+        <v>129805491</v>
       </c>
       <c r="B45" t="n">
-        <v>57895</v>
+        <v>57740</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5521,46 +5528,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>424548</v>
+        <v>424474</v>
       </c>
       <c r="R45" t="n">
-        <v>6957946</v>
+        <v>6957973</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5593,6 +5588,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5622,7 +5622,7 @@
         <v>129805502</v>
       </c>
       <c r="B46" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>129805516</v>
       </c>
       <c r="B47" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>129805512</v>
       </c>
       <c r="B48" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 49797-2025 artfynd.xlsx
+++ b/artfynd/A 49797-2025 artfynd.xlsx
@@ -5408,10 +5408,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129805515</v>
+        <v>129805491</v>
       </c>
       <c r="B44" t="n">
-        <v>57898</v>
+        <v>57740</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5419,46 +5419,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>424548</v>
+        <v>424474</v>
       </c>
       <c r="R44" t="n">
-        <v>6957946</v>
+        <v>6957973</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5491,6 +5479,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5517,10 +5510,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129805491</v>
+        <v>129805515</v>
       </c>
       <c r="B45" t="n">
-        <v>57740</v>
+        <v>57898</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5528,34 +5521,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>424474</v>
+        <v>424548</v>
       </c>
       <c r="R45" t="n">
-        <v>6957973</v>
+        <v>6957946</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5588,11 +5593,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 49797-2025 artfynd.xlsx
+++ b/artfynd/A 49797-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129797291</v>
+        <v>129797285</v>
       </c>
       <c r="B2" t="n">
         <v>57740</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424863</v>
+        <v>424331</v>
       </c>
       <c r="R2" t="n">
-        <v>6957889</v>
+        <v>6958001</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, men även några på gränsen till färska, på en gammal gran intill några tallågor.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,7 +810,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129797285</v>
+        <v>129797291</v>
       </c>
       <c r="B3" t="n">
         <v>57740</v>
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>424331</v>
+        <v>424863</v>
       </c>
       <c r="R3" t="n">
-        <v>6958001</v>
+        <v>6957889</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, men även några på gränsen till färska, på en gammal gran intill några tallågor.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1611,7 +1611,7 @@
         <v>129797296</v>
       </c>
       <c r="B9" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>129797299</v>
       </c>
       <c r="B10" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>129797295</v>
       </c>
       <c r="B12" t="n">
-        <v>80096</v>
+        <v>80097</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3896,10 +3896,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129805497</v>
+        <v>129805520</v>
       </c>
       <c r="B29" t="n">
-        <v>57740</v>
+        <v>91626</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,23 +3907,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3931,10 +3927,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>424480</v>
+        <v>424860</v>
       </c>
       <c r="R29" t="n">
-        <v>6958080</v>
+        <v>6957844</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3967,11 +3963,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3998,10 +3989,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129805520</v>
+        <v>129805497</v>
       </c>
       <c r="B30" t="n">
-        <v>91625</v>
+        <v>57740</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4009,19 +4000,23 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4029,10 +4024,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>424860</v>
+        <v>424480</v>
       </c>
       <c r="R30" t="n">
-        <v>6957844</v>
+        <v>6958080</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4065,6 +4060,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -5216,7 +5216,7 @@
         <v>129805519</v>
       </c>
       <c r="B42" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>129805516</v>
       </c>
       <c r="B47" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 49797-2025 artfynd.xlsx
+++ b/artfynd/A 49797-2025 artfynd.xlsx
@@ -3896,10 +3896,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129805520</v>
+        <v>129805497</v>
       </c>
       <c r="B29" t="n">
-        <v>91626</v>
+        <v>57740</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,19 +3907,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3927,10 +3931,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>424860</v>
+        <v>424480</v>
       </c>
       <c r="R29" t="n">
-        <v>6957844</v>
+        <v>6958080</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3963,6 +3967,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3989,10 +3998,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129805497</v>
+        <v>129805520</v>
       </c>
       <c r="B30" t="n">
-        <v>57740</v>
+        <v>91626</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4000,23 +4009,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4024,10 +4029,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>424480</v>
+        <v>424860</v>
       </c>
       <c r="R30" t="n">
-        <v>6958080</v>
+        <v>6957844</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4060,11 +4065,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 49797-2025 artfynd.xlsx
+++ b/artfynd/A 49797-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129797285</v>
+        <v>129797291</v>
       </c>
       <c r="B2" t="n">
         <v>57740</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424331</v>
+        <v>424863</v>
       </c>
       <c r="R2" t="n">
-        <v>6958001</v>
+        <v>6957889</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, men även några på gränsen till färska, på en gammal gran intill några tallågor.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,7 +810,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129797291</v>
+        <v>129797285</v>
       </c>
       <c r="B3" t="n">
         <v>57740</v>
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>424863</v>
+        <v>424331</v>
       </c>
       <c r="R3" t="n">
-        <v>6957889</v>
+        <v>6958001</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, men även några på gränsen till färska, på en gammal gran intill några tallågor.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1611,7 +1611,7 @@
         <v>129797296</v>
       </c>
       <c r="B9" t="n">
-        <v>80229</v>
+        <v>80230</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>129797299</v>
       </c>
       <c r="B10" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>129797295</v>
       </c>
       <c r="B12" t="n">
-        <v>80097</v>
+        <v>80098</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>129797294</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3896,10 +3896,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129805497</v>
+        <v>129805520</v>
       </c>
       <c r="B29" t="n">
-        <v>57740</v>
+        <v>91643</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,23 +3907,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3931,10 +3927,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>424480</v>
+        <v>424860</v>
       </c>
       <c r="R29" t="n">
-        <v>6958080</v>
+        <v>6957844</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3967,11 +3963,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3998,10 +3989,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129805520</v>
+        <v>129805497</v>
       </c>
       <c r="B30" t="n">
-        <v>91626</v>
+        <v>57740</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4009,19 +4000,23 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4029,10 +4024,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>424860</v>
+        <v>424480</v>
       </c>
       <c r="R30" t="n">
-        <v>6957844</v>
+        <v>6958080</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4065,6 +4060,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -5213,10 +5213,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129805519</v>
+        <v>129805500</v>
       </c>
       <c r="B42" t="n">
-        <v>91626</v>
+        <v>57740</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,19 +5224,23 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5244,10 +5248,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>424761</v>
+        <v>424455</v>
       </c>
       <c r="R42" t="n">
-        <v>6957912</v>
+        <v>6958082</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5280,6 +5284,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5306,10 +5315,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129805500</v>
+        <v>129805519</v>
       </c>
       <c r="B43" t="n">
-        <v>57740</v>
+        <v>91643</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5317,23 +5326,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5341,10 +5346,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>424455</v>
+        <v>424761</v>
       </c>
       <c r="R43" t="n">
-        <v>6958082</v>
+        <v>6957912</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5377,11 +5382,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5513,7 +5513,7 @@
         <v>129805515</v>
       </c>
       <c r="B45" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>129805516</v>
       </c>
       <c r="B47" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 49797-2025 artfynd.xlsx
+++ b/artfynd/A 49797-2025 artfynd.xlsx
@@ -1338,7 +1338,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129797293</v>
+        <v>129797288</v>
       </c>
       <c r="B7" t="n">
         <v>57741</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>424901</v>
+        <v>424643</v>
       </c>
       <c r="R7" t="n">
-        <v>6957647</v>
+        <v>6958012</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall.</t>
+          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129797288</v>
+        <v>129797293</v>
       </c>
       <c r="B8" t="n">
         <v>57741</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>424643</v>
+        <v>424901</v>
       </c>
       <c r="R8" t="n">
-        <v>6958012</v>
+        <v>6957647</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
+          <t>Ringhack, äldre, på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1570,17 +1570,17 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129805491</v>
+        <v>129805515</v>
       </c>
       <c r="B44" t="n">
-        <v>57741</v>
+        <v>57900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5419,34 +5419,46 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>424474</v>
+        <v>424548</v>
       </c>
       <c r="R44" t="n">
-        <v>6957973</v>
+        <v>6957946</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5479,11 +5491,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5510,10 +5517,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129805515</v>
+        <v>129805491</v>
       </c>
       <c r="B45" t="n">
-        <v>57900</v>
+        <v>57741</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5521,46 +5528,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>424548</v>
+        <v>424474</v>
       </c>
       <c r="R45" t="n">
-        <v>6957946</v>
+        <v>6957973</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5593,6 +5588,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 49797-2025 artfynd.xlsx
+++ b/artfynd/A 49797-2025 artfynd.xlsx
@@ -1746,7 +1746,7 @@
         <v>129797299</v>
       </c>
       <c r="B10" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129805503</v>
+        <v>129805493</v>
       </c>
       <c r="B17" t="n">
         <v>57741</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>424507</v>
+        <v>424319</v>
       </c>
       <c r="R17" t="n">
-        <v>6958067</v>
+        <v>6958042</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2770,7 +2770,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129805493</v>
+        <v>129805487</v>
       </c>
       <c r="B18" t="n">
         <v>57741</v>
@@ -2805,10 +2805,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>424319</v>
+        <v>424741</v>
       </c>
       <c r="R18" t="n">
-        <v>6958042</v>
+        <v>6957878</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2872,7 +2872,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129805487</v>
+        <v>129805503</v>
       </c>
       <c r="B19" t="n">
         <v>57741</v>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>424741</v>
+        <v>424507</v>
       </c>
       <c r="R19" t="n">
-        <v>6957878</v>
+        <v>6958067</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3590,7 +3590,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129805486</v>
+        <v>129805513</v>
       </c>
       <c r="B26" t="n">
         <v>57741</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>424588</v>
+        <v>424735</v>
       </c>
       <c r="R26" t="n">
-        <v>6957887</v>
+        <v>6957898</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gammalt bohål 2m upp i klen asp</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3692,7 +3692,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129805513</v>
+        <v>129805486</v>
       </c>
       <c r="B27" t="n">
         <v>57741</v>
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>424735</v>
+        <v>424588</v>
       </c>
       <c r="R27" t="n">
-        <v>6957898</v>
+        <v>6957887</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gammalt bohål 2m upp i klen asp</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3899,7 +3899,7 @@
         <v>129805520</v>
       </c>
       <c r="B29" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129805501</v>
+        <v>129805490</v>
       </c>
       <c r="B40" t="n">
         <v>57741</v>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>424430</v>
+        <v>424603</v>
       </c>
       <c r="R40" t="n">
-        <v>6958097</v>
+        <v>6957917</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5111,7 +5111,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129805490</v>
+        <v>129805501</v>
       </c>
       <c r="B41" t="n">
         <v>57741</v>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>424603</v>
+        <v>424430</v>
       </c>
       <c r="R41" t="n">
-        <v>6957917</v>
+        <v>6958097</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack äldre på tall</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5213,10 +5213,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129805519</v>
+        <v>129805500</v>
       </c>
       <c r="B42" t="n">
-        <v>91659</v>
+        <v>57741</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,19 +5224,23 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5244,10 +5248,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>424761</v>
+        <v>424455</v>
       </c>
       <c r="R42" t="n">
-        <v>6957912</v>
+        <v>6958082</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5280,6 +5284,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5306,10 +5315,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129805500</v>
+        <v>129805519</v>
       </c>
       <c r="B43" t="n">
-        <v>57741</v>
+        <v>91661</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5317,23 +5326,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5341,10 +5346,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>424455</v>
+        <v>424761</v>
       </c>
       <c r="R43" t="n">
-        <v>6958082</v>
+        <v>6957912</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5377,11 +5382,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5724,7 +5724,7 @@
         <v>129805516</v>
       </c>
       <c r="B47" t="n">
-        <v>91660</v>
+        <v>91662</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 49797-2025 artfynd.xlsx
+++ b/artfynd/A 49797-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129797291</v>
+        <v>129805516</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424863</v>
+        <v>424426</v>
       </c>
       <c r="R2" t="n">
-        <v>6957889</v>
+        <v>6958107</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +748,6 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -769,83 +756,53 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129797285</v>
+        <v>129797300</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -853,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>424331</v>
+        <v>424405</v>
       </c>
       <c r="R3" t="n">
-        <v>6958001</v>
+        <v>6957936</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,25 +848,16 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, men även några på gränsen till färska, på en gammal gran intill några tallågor.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>gran</t>
@@ -922,12 +870,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -945,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129797297</v>
+        <v>129797295</v>
       </c>
       <c r="B4" t="n">
-        <v>57845</v>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -956,50 +904,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>424801</v>
+        <v>424583</v>
       </c>
       <c r="R4" t="n">
-        <v>6957800</v>
+        <v>6957891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1036,7 +971,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Synobservation av 5 st lavskrikor i äldre gles tallskog.</t>
+          <t>På en gammal asp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,12 +980,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1068,40 +1024,39 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129797283</v>
+        <v>129797296</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>80468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1111,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>424427</v>
+        <v>424581</v>
       </c>
       <c r="R5" t="n">
-        <v>6957961</v>
+        <v>6957890</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1151,7 +1106,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>En granhögstubbe (med vedsvamp) med 6 st gamla bohål efter hackspettar. Ett bohål med mindre dimension finns på 11 dm höjd över marken och är mest troligt bohål efter tretåig hackspett.</t>
+          <t>På en gammal asp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,6 +1115,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1170,22 +1126,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,27 +1159,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129797284</v>
+        <v>129805517</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1234,11 +1190,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1246,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>424412</v>
+        <v>424426</v>
       </c>
       <c r="R6" t="n">
-        <v>6957972</v>
+        <v>6958107</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1286,7 +1238,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran med full längd och 33 cm i brösthöjdsdiameter.</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,51 +1249,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129797288</v>
+        <v>129797283</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1298,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1381,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>424643</v>
+        <v>424427</v>
       </c>
       <c r="R7" t="n">
-        <v>6958012</v>
+        <v>6957961</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1421,7 +1348,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
+          <t>En granhögstubbe (med vedsvamp) med 6 st gamla bohål efter hackspettar. Ett bohål med mindre dimension finns på 11 dm höjd över marken och är mest troligt bohål efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1450,12 +1377,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1473,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129797293</v>
+        <v>129797284</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1516,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>424901</v>
+        <v>424412</v>
       </c>
       <c r="R8" t="n">
-        <v>6957647</v>
+        <v>6957972</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1556,7 +1483,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall.</t>
+          <t>Ringhack, äldre, på en stående död gran med full längd och 33 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1570,27 +1497,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1608,39 +1535,40 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129797296</v>
+        <v>129797285</v>
       </c>
       <c r="B9" t="n">
-        <v>80236</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1650,10 +1578,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>424581</v>
+        <v>424331</v>
       </c>
       <c r="R9" t="n">
-        <v>6957890</v>
+        <v>6958001</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1690,7 +1618,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en gammal asp.</t>
+          <t>Ringhack, äldre, men även några på gränsen till färska, på en gammal gran intill några tallågor.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1699,7 +1627,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1710,22 +1637,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1743,10 +1670,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129797299</v>
+        <v>129797286</v>
       </c>
       <c r="B10" t="n">
-        <v>91661</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1754,24 +1681,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1781,10 +1713,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>424431</v>
+        <v>424591</v>
       </c>
       <c r="R10" t="n">
-        <v>6957958</v>
+        <v>6958093</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1821,7 +1753,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en granhögstubbe med bohål.</t>
+          <t>Ringhack, färska och äldre, i riklig mängd längs minst 3 meter på en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1830,7 +1762,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1851,12 +1782,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1877,7 +1808,7 @@
         <v>129797287</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2009,37 +1940,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129797295</v>
+        <v>129797288</v>
       </c>
       <c r="B12" t="n">
-        <v>80104</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2047,10 +1983,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>424583</v>
+        <v>424643</v>
       </c>
       <c r="R12" t="n">
-        <v>6957891</v>
+        <v>6958012</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2087,7 +2023,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På en gammal asp.</t>
+          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2096,7 +2032,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2107,22 +2042,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2143,7 +2078,7 @@
         <v>129797289</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2275,10 +2210,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129797294</v>
+        <v>129797290</v>
       </c>
       <c r="B14" t="n">
-        <v>57900</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2286,50 +2221,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>424533</v>
+        <v>424826</v>
       </c>
       <c r="R14" t="n">
-        <v>6958077</v>
+        <v>6957894</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2366,7 +2293,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Minst 1 individ med lockläte i flerskiktad granskog med smala björkhögstubbar.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2380,7 +2307,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2398,10 +2345,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129797292</v>
+        <v>129797291</v>
       </c>
       <c r="B15" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2441,10 +2388,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>424902</v>
+        <v>424863</v>
       </c>
       <c r="R15" t="n">
-        <v>6957650</v>
+        <v>6957889</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2481,7 +2428,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2495,17 +2442,17 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -2515,7 +2462,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2533,10 +2480,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129797290</v>
+        <v>129797292</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2576,10 +2523,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>424826</v>
+        <v>424902</v>
       </c>
       <c r="R16" t="n">
-        <v>6957894</v>
+        <v>6957650</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2616,7 +2563,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2630,17 +2577,17 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -2650,7 +2597,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2668,10 +2615,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129805493</v>
+        <v>129797293</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2697,16 +2644,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>424319</v>
+        <v>424901</v>
       </c>
       <c r="R17" t="n">
-        <v>6958042</v>
+        <v>6957647</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2743,7 +2698,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2754,26 +2709,51 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129805487</v>
+        <v>129805486</v>
       </c>
       <c r="B18" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2805,10 +2785,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>424741</v>
+        <v>424588</v>
       </c>
       <c r="R18" t="n">
-        <v>6957878</v>
+        <v>6957887</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2845,14 +2825,14 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Gammalt bohål 2m upp i klen asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG18" t="b">
         <v>0</v>
@@ -2872,10 +2852,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129805503</v>
+        <v>129805487</v>
       </c>
       <c r="B19" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2907,10 +2887,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>424507</v>
+        <v>424741</v>
       </c>
       <c r="R19" t="n">
-        <v>6958067</v>
+        <v>6957878</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2947,7 +2927,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre på tall</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2974,10 +2954,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129805517</v>
+        <v>129805488</v>
       </c>
       <c r="B20" t="n">
-        <v>57738</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2985,16 +2965,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3003,20 +2983,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>424426</v>
+        <v>424434</v>
       </c>
       <c r="R20" t="n">
-        <v>6958107</v>
+        <v>6957942</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3053,7 +3029,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3080,10 +3056,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129805508</v>
+        <v>129805490</v>
       </c>
       <c r="B21" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3115,10 +3091,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>424626</v>
+        <v>424603</v>
       </c>
       <c r="R21" t="n">
-        <v>6957996</v>
+        <v>6957917</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3182,10 +3158,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129805504</v>
+        <v>129805491</v>
       </c>
       <c r="B22" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,10 +3193,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>424513</v>
+        <v>424474</v>
       </c>
       <c r="R22" t="n">
-        <v>6958070</v>
+        <v>6957973</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3284,10 +3260,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129805511</v>
+        <v>129805492</v>
       </c>
       <c r="B23" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3319,10 +3295,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>424758</v>
+        <v>424403</v>
       </c>
       <c r="R23" t="n">
-        <v>6957908</v>
+        <v>6958029</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3359,7 +3335,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3386,10 +3362,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129805506</v>
+        <v>129805493</v>
       </c>
       <c r="B24" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3421,10 +3397,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>424593</v>
+        <v>424319</v>
       </c>
       <c r="R24" t="n">
-        <v>6958056</v>
+        <v>6958042</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3461,7 +3437,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3488,10 +3464,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129805488</v>
+        <v>129805494</v>
       </c>
       <c r="B25" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3523,10 +3499,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>424434</v>
+        <v>424372</v>
       </c>
       <c r="R25" t="n">
-        <v>6957942</v>
+        <v>6958049</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3590,10 +3566,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129805513</v>
+        <v>129805495</v>
       </c>
       <c r="B26" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3625,10 +3601,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>424735</v>
+        <v>424572</v>
       </c>
       <c r="R26" t="n">
-        <v>6957898</v>
+        <v>6958078</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3665,7 +3641,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3692,10 +3668,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129805486</v>
+        <v>129805496</v>
       </c>
       <c r="B27" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3727,10 +3703,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>424588</v>
+        <v>424489</v>
       </c>
       <c r="R27" t="n">
-        <v>6957887</v>
+        <v>6958088</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3767,14 +3743,14 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Gammalt bohål 2m upp i klen asp</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>
@@ -3794,10 +3770,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129805514</v>
+        <v>129805497</v>
       </c>
       <c r="B28" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3829,10 +3805,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>424899</v>
+        <v>424480</v>
       </c>
       <c r="R28" t="n">
-        <v>6957678</v>
+        <v>6958080</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3896,10 +3872,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129805520</v>
+        <v>129805498</v>
       </c>
       <c r="B29" t="n">
-        <v>91661</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3907,19 +3883,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3927,10 +3907,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>424860</v>
+        <v>424462</v>
       </c>
       <c r="R29" t="n">
-        <v>6957844</v>
+        <v>6958065</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3963,6 +3943,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3989,10 +3974,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129805497</v>
+        <v>129805500</v>
       </c>
       <c r="B30" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4024,10 +4009,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>424480</v>
+        <v>424455</v>
       </c>
       <c r="R30" t="n">
-        <v>6958080</v>
+        <v>6958082</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4091,10 +4076,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129805492</v>
+        <v>129805501</v>
       </c>
       <c r="B31" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4126,10 +4111,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>424403</v>
+        <v>424430</v>
       </c>
       <c r="R31" t="n">
-        <v>6958029</v>
+        <v>6958097</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4166,7 +4151,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4193,10 +4178,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129805496</v>
+        <v>129805502</v>
       </c>
       <c r="B32" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4228,10 +4213,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>424489</v>
+        <v>424416</v>
       </c>
       <c r="R32" t="n">
-        <v>6958088</v>
+        <v>6958115</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4268,7 +4253,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4295,10 +4280,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129805494</v>
+        <v>129805503</v>
       </c>
       <c r="B33" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4330,10 +4315,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>424372</v>
+        <v>424507</v>
       </c>
       <c r="R33" t="n">
-        <v>6958049</v>
+        <v>6958067</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4370,7 +4355,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4397,10 +4382,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129805498</v>
+        <v>129805504</v>
       </c>
       <c r="B34" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4432,10 +4417,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>424462</v>
+        <v>424513</v>
       </c>
       <c r="R34" t="n">
-        <v>6958065</v>
+        <v>6958070</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4502,7 +4487,7 @@
         <v>129805505</v>
       </c>
       <c r="B35" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4601,10 +4586,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129805495</v>
+        <v>129805506</v>
       </c>
       <c r="B36" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4636,10 +4621,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>424572</v>
+        <v>424593</v>
       </c>
       <c r="R36" t="n">
-        <v>6958078</v>
+        <v>6958056</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4703,10 +4688,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129805509</v>
+        <v>129805507</v>
       </c>
       <c r="B37" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4738,10 +4723,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>424763</v>
+        <v>424614</v>
       </c>
       <c r="R37" t="n">
-        <v>6957936</v>
+        <v>6957999</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4778,7 +4763,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4805,10 +4790,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129805507</v>
+        <v>129805508</v>
       </c>
       <c r="B38" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4840,10 +4825,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>424614</v>
+        <v>424626</v>
       </c>
       <c r="R38" t="n">
-        <v>6957999</v>
+        <v>6957996</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4907,10 +4892,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129805510</v>
+        <v>129805509</v>
       </c>
       <c r="B39" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4942,10 +4927,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>424762</v>
+        <v>424763</v>
       </c>
       <c r="R39" t="n">
-        <v>6957913</v>
+        <v>6957936</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4982,7 +4967,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5009,10 +4994,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129805490</v>
+        <v>129805510</v>
       </c>
       <c r="B40" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5044,10 +5029,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>424603</v>
+        <v>424762</v>
       </c>
       <c r="R40" t="n">
-        <v>6957917</v>
+        <v>6957913</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5084,7 +5069,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre på tall</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5111,10 +5096,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129805501</v>
+        <v>129805511</v>
       </c>
       <c r="B41" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5146,10 +5131,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>424430</v>
+        <v>424758</v>
       </c>
       <c r="R41" t="n">
-        <v>6958097</v>
+        <v>6957908</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5213,10 +5198,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129805500</v>
+        <v>129805512</v>
       </c>
       <c r="B42" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5248,10 +5233,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>424455</v>
+        <v>424748</v>
       </c>
       <c r="R42" t="n">
-        <v>6958082</v>
+        <v>6957908</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5315,10 +5300,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129805519</v>
+        <v>129805513</v>
       </c>
       <c r="B43" t="n">
-        <v>91661</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5326,19 +5311,23 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5346,10 +5335,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>424761</v>
+        <v>424735</v>
       </c>
       <c r="R43" t="n">
-        <v>6957912</v>
+        <v>6957898</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5382,6 +5371,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5408,10 +5402,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129805515</v>
+        <v>129805514</v>
       </c>
       <c r="B44" t="n">
-        <v>57900</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5419,46 +5413,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>424548</v>
+        <v>424899</v>
       </c>
       <c r="R44" t="n">
-        <v>6957946</v>
+        <v>6957678</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5491,6 +5473,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5517,10 +5504,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129805491</v>
+        <v>75706640</v>
       </c>
       <c r="B45" t="n">
-        <v>57741</v>
+        <v>5495</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5528,21 +5515,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>101410</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5552,10 +5539,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>424474</v>
+        <v>424995</v>
       </c>
       <c r="R45" t="n">
-        <v>6957973</v>
+        <v>6957816</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5582,17 +5569,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2018-10-02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2018-10-02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5603,26 +5585,36 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Tall, barrnaturskog</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129805502</v>
+        <v>129797294</v>
       </c>
       <c r="B46" t="n">
-        <v>57741</v>
+        <v>58114</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5630,34 +5622,50 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>424416</v>
+        <v>424533</v>
       </c>
       <c r="R46" t="n">
-        <v>6958115</v>
+        <v>6958077</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5694,7 +5702,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Minst 1 individ med lockläte i flerskiktad granskog med smala björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5705,26 +5713,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129805516</v>
+        <v>129805515</v>
       </c>
       <c r="B47" t="n">
-        <v>91662</v>
+        <v>58114</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5732,34 +5745,46 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>424426</v>
+        <v>424548</v>
       </c>
       <c r="R47" t="n">
-        <v>6958107</v>
+        <v>6957946</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5818,10 +5843,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129805512</v>
+        <v>129797297</v>
       </c>
       <c r="B48" t="n">
-        <v>57741</v>
+        <v>58057</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5829,16 +5854,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5846,17 +5871,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lövsta, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>424748</v>
+        <v>424801</v>
       </c>
       <c r="R48" t="n">
-        <v>6957908</v>
+        <v>6957800</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5893,7 +5934,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Synobservation av 5 st lavskrikor i äldre gles tallskog.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5904,16 +5945,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 49797-2025 artfynd.xlsx
+++ b/artfynd/A 49797-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805516</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797300</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797295</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797296</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1262,6 +1287,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805517</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1397,6 +1427,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797283</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1532,6 +1567,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797284</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1667,6 +1707,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797285</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1802,6 +1847,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797286</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1937,6 +1987,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797287</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2072,6 +2127,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797288</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2207,6 +2267,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797289</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2342,6 +2407,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797290</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2477,6 +2547,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797291</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2612,6 +2687,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797292</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2747,6 +2827,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797293</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2849,6 +2934,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805486</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2951,6 +3041,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805487</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3053,6 +3148,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805488</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3155,6 +3255,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805490</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3257,6 +3362,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805491</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3359,6 +3469,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805492</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3461,6 +3576,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805493</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3563,6 +3683,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805494</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3665,6 +3790,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805495</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3767,6 +3897,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805496</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3869,6 +4004,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805497</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3971,6 +4111,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805498</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4073,6 +4218,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805500</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4175,6 +4325,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805501</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4277,6 +4432,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805502</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4379,6 +4539,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805503</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4481,6 +4646,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805504</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4583,6 +4753,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805505</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4685,6 +4860,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805506</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4787,6 +4967,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805507</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4889,6 +5074,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805508</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4991,6 +5181,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805509</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5093,6 +5288,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805510</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5195,6 +5395,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805511</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5297,6 +5502,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805512</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5399,6 +5609,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805513</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5501,6 +5716,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805514</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5608,6 +5828,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75706640</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5731,6 +5956,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797294</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5840,6 +6070,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805515</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5963,8 +6198,62 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797297</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>